--- a/Weekly_Performance_Report_VN.xlsx
+++ b/Weekly_Performance_Report_VN.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,16 +42,22 @@
     <t>寄样支出总和</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-01-19-16_24.csv</t>
-  </si>
-  <si>
-    <t>全部 笔订单-2026-01-19-18_22.csv</t>
-  </si>
-  <si>
-    <t>18/01/2026</t>
-  </si>
-  <si>
-    <t>11/01/2026</t>
+    <t>全部 笔订单-2026-01-21-18_37.csv</t>
+  </si>
+  <si>
+    <t>全部 笔订单-2026-01-21-18_39.csv</t>
+  </si>
+  <si>
+    <t>全部 笔订单-2026-01-22-18_43.csv</t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
   </si>
   <si>
     <t>日期</t>
@@ -84,12 +90,12 @@
     <t>身体乳</t>
   </si>
   <si>
+    <t>防晒霜</t>
+  </si>
+  <si>
     <t>身体乳300ml</t>
   </si>
   <si>
-    <t>防晒霜</t>
-  </si>
-  <si>
     <t>产品名称</t>
   </si>
   <si>
@@ -102,22 +108,10 @@
     <t>身体乳双瓶</t>
   </si>
   <si>
-    <t>身体乳三瓶</t>
-  </si>
-  <si>
     <t>防晒霜单瓶</t>
   </si>
   <si>
     <t>精华液单瓶</t>
-  </si>
-  <si>
-    <t>精华液双瓶</t>
-  </si>
-  <si>
-    <t>精华液三瓶</t>
-  </si>
-  <si>
-    <t>精华液&amp;黑鸦片</t>
   </si>
 </sst>
 </file>
@@ -475,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -509,25 +503,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>9275679</v>
+        <v>1407715</v>
       </c>
       <c r="D2">
-        <v>2576.58</v>
+        <v>391.03</v>
       </c>
       <c r="E2">
-        <v>8016383</v>
+        <v>1210855</v>
       </c>
       <c r="F2">
-        <v>796.9899999999999</v>
+        <v>120.01</v>
       </c>
       <c r="G2">
-        <v>475.8799999999999</v>
+        <v>68.86</v>
       </c>
       <c r="H2">
-        <v>383.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -535,25 +529,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>16088769</v>
+        <v>1223753</v>
       </c>
       <c r="D3">
-        <v>4469.1</v>
+        <v>339.93</v>
       </c>
       <c r="E3">
-        <v>13144950</v>
+        <v>1160703</v>
       </c>
       <c r="F3">
-        <v>1347.4</v>
+        <v>105.7</v>
       </c>
       <c r="G3">
-        <v>648.3900000000001</v>
+        <v>64.53</v>
       </c>
       <c r="H3">
-        <v>262.73</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>623994</v>
+      </c>
+      <c r="D4">
+        <v>173.33</v>
+      </c>
+      <c r="E4">
+        <v>575494</v>
+      </c>
+      <c r="F4">
+        <v>59.23999999999999</v>
+      </c>
+      <c r="G4">
+        <v>39.35</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -568,28 +588,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -597,25 +617,25 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>9024837</v>
+        <v>336326</v>
       </c>
       <c r="D2">
-        <v>2506.9</v>
+        <v>93.42</v>
       </c>
       <c r="E2">
-        <v>6882738</v>
+        <v>296326</v>
       </c>
       <c r="F2">
-        <v>703.78</v>
+        <v>18.04</v>
       </c>
       <c r="G2">
-        <v>245.46</v>
+        <v>6.42</v>
       </c>
       <c r="H2">
-        <v>262.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,22 +643,22 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>6249334</v>
+        <v>968590</v>
       </c>
       <c r="D3">
-        <v>1735.93</v>
+        <v>269.05</v>
       </c>
       <c r="E3">
-        <v>5473714</v>
+        <v>811730</v>
       </c>
       <c r="F3">
-        <v>608.4</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G3">
-        <v>384.4499999999999</v>
+        <v>59.29</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -649,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>609000</v>
+        <v>102799</v>
       </c>
       <c r="D4">
-        <v>169.17</v>
+        <v>28.56</v>
       </c>
       <c r="E4">
-        <v>582900</v>
+        <v>102799</v>
       </c>
       <c r="F4">
-        <v>18.48</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G4">
-        <v>12.18</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -672,25 +692,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>205598</v>
+        <v>168163</v>
       </c>
       <c r="D5">
-        <v>57.11</v>
+        <v>46.71</v>
       </c>
       <c r="E5">
-        <v>205598</v>
+        <v>168163</v>
       </c>
       <c r="F5">
-        <v>16.74</v>
+        <v>9.02</v>
       </c>
       <c r="G5">
-        <v>6.3</v>
+        <v>3.21</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -698,51 +718,51 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>2337149</v>
+        <v>968590</v>
       </c>
       <c r="D6">
-        <v>649.21</v>
+        <v>269.05</v>
       </c>
       <c r="E6">
-        <v>2162149</v>
+        <v>905540</v>
       </c>
       <c r="F6">
-        <v>135.52</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G6">
-        <v>57.63</v>
+        <v>59.29</v>
       </c>
       <c r="H6">
-        <v>383.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>6369133</v>
+        <v>87000</v>
       </c>
       <c r="D7">
-        <v>1769.2</v>
+        <v>24.17</v>
       </c>
       <c r="E7">
-        <v>5350937</v>
+        <v>87000</v>
       </c>
       <c r="F7">
-        <v>627.12</v>
+        <v>3.08</v>
       </c>
       <c r="G7">
-        <v>402.7099999999999</v>
+        <v>2.03</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -750,25 +770,25 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>261000</v>
+        <v>536994</v>
       </c>
       <c r="D8">
-        <v>72.5</v>
+        <v>149.16</v>
       </c>
       <c r="E8">
-        <v>194900</v>
+        <v>488494</v>
       </c>
       <c r="F8">
-        <v>9.24</v>
+        <v>56.16</v>
       </c>
       <c r="G8">
-        <v>6.09</v>
+        <v>37.32</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -776,25 +796,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9">
-        <v>308397</v>
+        <v>87000</v>
       </c>
       <c r="D9">
-        <v>85.67</v>
+        <v>24.17</v>
       </c>
       <c r="E9">
-        <v>308397</v>
+        <v>87000</v>
       </c>
       <c r="F9">
-        <v>25.11</v>
+        <v>3.08</v>
       </c>
       <c r="G9">
-        <v>9.449999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -807,117 +827,91 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>59</v>
-      </c>
-      <c r="C3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
+      <c r="D6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
